--- a/inst/testdata/registryid/frs_testpoints_10.xlsx
+++ b/inst/testdata/registryid/frs_testpoints_10.xlsx
@@ -11,6 +11,17 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>REGISTRY_ID</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,96 +365,92 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>REGISTRY_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>110040663047</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>110040535702</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>110070353219</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>110070364858</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>110040784933</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>110040713948</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>110071956718</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>110071377973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>110054114061</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>110053728276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>110031411719</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>110031317518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>110041513957</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>110041466053</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>110038511820</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>110038355954</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110070272516</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>110070281222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>110070312330</v>
+        <v>110071844351</v>
       </c>
     </row>
   </sheetData>
